--- a/artfynd/S 7747-2021 artfynd.xlsx
+++ b/artfynd/S 7747-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105074880</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106442179</t>
         </is>
       </c>
     </row>
@@ -1010,6 +1025,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95378159</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036350</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036348</t>
         </is>
       </c>
     </row>
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95378156</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1425,6 +1460,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036346</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1526,6 +1566,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036347</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1632,6 +1677,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105074899</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1743,6 +1793,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105074924</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106442176</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1965,6 +2025,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95378164</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2071,6 +2136,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105074908</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2182,6 +2252,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105074934</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2298,6 +2373,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95378165</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2405,6 +2485,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79382582</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2526,6 +2611,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95378148</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2632,6 +2722,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105074906</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2743,6 +2838,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105074931</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2849,6 +2949,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106442178</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2956,6 +3061,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79382580</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3077,6 +3187,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95378141</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3183,6 +3298,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105074907</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3294,6 +3414,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105074933</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3400,6 +3525,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106442180</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3506,6 +3636,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105074912</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3617,6 +3752,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105074938</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3723,6 +3863,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105074887</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3834,6 +3979,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105074932</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3950,6 +4100,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95378178</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4051,6 +4206,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036352</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4157,6 +4317,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105074911</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4268,6 +4433,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105074937</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4375,6 +4545,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79382581</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4491,6 +4666,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95378151</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4592,6 +4772,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036356</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4698,6 +4883,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105074917</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4809,6 +4999,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105074940</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4915,6 +5110,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106442182</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5027,6 +5227,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95378168</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5134,6 +5339,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105074889</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5241,6 +5451,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105074920</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5349,6 +5564,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105074941</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5460,6 +5680,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105074973</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5567,8 +5792,60 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105074921</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>